--- a/Financial Analysis/HO.xlsx
+++ b/Financial Analysis/HO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7932B05-A193-4587-B451-E7C6BDB461E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BFCBB37-F7A2-4B71-AB8B-5D813227F99B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BF427BEE-D598-4325-938D-FB62EE8A4E7D}"/>
   </bookViews>
@@ -770,14 +770,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>271</v>
+        <v>226.9</v>
       </c>
       <c r="E3" s="4">
-        <v>45934</v>
+        <v>45983</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45934</v>
+        <v>45983</v>
       </c>
       <c r="G3" s="4">
         <v>45953</v>
@@ -801,7 +801,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>55663.4</v>
+        <v>46605.26</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -843,7 +843,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>57071.5</v>
+        <v>48013.36</v>
       </c>
     </row>
   </sheetData>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="AD37" s="11">
         <f>Main!D3</f>
-        <v>271</v>
+        <v>226.9</v>
       </c>
     </row>
     <row r="38" spans="2:30" x14ac:dyDescent="0.3">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="AD38" s="12">
         <f>AD36/AD37-1</f>
-        <v>-0.59343933080112277</v>
+        <v>-0.51442070800839268</v>
       </c>
     </row>
     <row r="39" spans="2:30" x14ac:dyDescent="0.3">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="G42" s="15">
         <f>Main!D9/Model!G40</f>
-        <v>1.4676241417440277</v>
+        <v>1.2346892277624912</v>
       </c>
     </row>
     <row r="43" spans="2:30" x14ac:dyDescent="0.3">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="G43" s="10">
         <f>G40/Main!D9-1</f>
-        <v>-0.31862663501046928</v>
+        <v>-0.19007959451286061</v>
       </c>
     </row>
   </sheetData>
